--- a/notebooks/phase II/data/Part Naming Structure by Commodity.xlsx
+++ b/notebooks/phase II/data/Part Naming Structure by Commodity.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29101"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dana.siniard\Diverzify\Procurement Data Files - General\Crowe\Part Clean-Up\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nzhuw\OneDrive\Desktop\10. Application Development\Diverzify\diverzify_freight_analysis\notebooks\phase II\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{E400FCF4-DD2B-46BF-A398-AF7526F86B7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0FC39DC9-E963-46AA-99C8-8AEF0A7ACF1B}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D2781FF-8F71-4D16-976A-667D99475553}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" xr2:uid="{6742DE92-15B1-4A9A-AA56-FAD30E9D62AC}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15990" firstSheet="1" xr2:uid="{6742DE92-15B1-4A9A-AA56-FAD30E9D62AC}"/>
   </bookViews>
   <sheets>
     <sheet name="Part Description Examples" sheetId="3" r:id="rId1"/>
     <sheet name="Notes" sheetId="4" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191028" refMode="R1C1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="51">
   <si>
     <t>General Part Information</t>
   </si>
@@ -118,6 +118,174 @@
     </r>
   </si>
   <si>
+    <t>Ecore E-grip III Adhesive 4gal</t>
+  </si>
+  <si>
+    <t>Teknoflor Prevail 4000 Two Part Epoxy Adhesive (EX4000) 1gal</t>
+  </si>
+  <si>
+    <r>
+      <t>Base</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> – Other Relevant Information is gauge (thickness).  Additionally, we need to know the type (profile) of the base, the length, and if it is coils or pieces.  It is important to include the style# as it determines which type (profile) it is.</t>
+    </r>
+  </si>
+  <si>
+    <t>Johnsonite Perceptions Recess (RWDC-XX) Cove Coil 4.25in x 120ft x 1/8in - Fawn (80)</t>
+  </si>
+  <si>
+    <t>Johnsonite Duracove Thermoplastic Rubber (DC-XX) Cove Pieces 6in x 4ft x 1/8in - Black (40)</t>
+  </si>
+  <si>
+    <t>Roppe Vinyl Wall Base Cove Pieces 4in x 4ft x 0.080in - White (170)</t>
+  </si>
+  <si>
+    <t>Mannington Edge Effects Cetera (EECET) Pieces 4in x 8ft x 5/16in - Jackalope (190)</t>
+  </si>
+  <si>
+    <r>
+      <t>Carpet (Broadloom)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> – Other Relevant Information is Backing, usually only a single size (width) provided.</t>
+    </r>
+  </si>
+  <si>
+    <t>Shaw Modify (5A204) 12ft Classicbac – Horizon (03496)</t>
+  </si>
+  <si>
+    <t>Mannington Gaskell 12ft 6in UltraBac RE – Debussy (42114)</t>
+  </si>
+  <si>
+    <t>Mohawk Eden Terrace (BC588) 12ft Weldlok – Twilight (575)</t>
+  </si>
+  <si>
+    <r>
+      <t>Carpet Tile</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> - Other Relevant Information is Backing, two sizes should be provided (L x W)</t>
+    </r>
+  </si>
+  <si>
+    <t>Shaw Habitat Tile (5T390) 9in x 36in Ecoworx - Still (88481)</t>
+  </si>
+  <si>
+    <t>Mohawk Stone Community (GT472) 12in x 36in EcoFlex ONE - Stone (949)</t>
+  </si>
+  <si>
+    <t>Flor Made You Look 50cm x 50cm CQuestGB - Ocean</t>
+  </si>
+  <si>
+    <r>
+      <t>Ceramic</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> – Other Relevant Information is Finish, but we also include what type of tile it is (field tile, bullnose, cove base, etc.).  Field tile often doesn’t have a style number, but sometimes the trim pieces do.  If there is a single item code for the piece, we would put it at the end as the color#.</t>
+    </r>
+  </si>
+  <si>
+    <t>TileBar Stonework Peak Field Tile 12in x 24in Satin - Black Jade</t>
+  </si>
+  <si>
+    <t>American Olean Color Story Cove Base Corner Left (SCL3361) 3in x 6in Glossy - Ice White (0025)</t>
+  </si>
+  <si>
+    <t>Daltile Advantage Field Tile 12in x 12in Matte - Mural Taupe (AQ02)</t>
+  </si>
+  <si>
+    <t>Daltile Synchronic Bullnose (P43F9) 3in x 24in Matte - White (SY30)</t>
+  </si>
+  <si>
+    <t>Floor &amp; Decor Hexagon Marble Mosaic 12in x 12in sheet Polished - Bianco Carrara (931100750)</t>
+  </si>
+  <si>
+    <r>
+      <t>Rubber Rolls</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> - Other Relevant Information is thickness (if provided), usually single size (width).</t>
+    </r>
+  </si>
+  <si>
+    <t>Mondo Super X Performance 8MM 3ft 4in - Grey (P31)</t>
+  </si>
+  <si>
+    <t>Nora Noraplan Convia 48in 2.0MM - Pearl Grey (7351)</t>
+  </si>
+  <si>
+    <r>
+      <t>Rubber Tile</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> - Other Relevant Information is thickness (if provided), two sizes (L x W).</t>
+    </r>
+  </si>
+  <si>
+    <t>North West Rubber Ultimate Zip Tile 28.5in x 28.5in 9MM - Grey (5520400)</t>
+  </si>
+  <si>
+    <t>Mondo Sport Impact 6MM 36in x 36in Purple (026)</t>
+  </si>
+  <si>
+    <r>
+      <t>Transitions</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> – Other Relevant Information is generally not used.</t>
+    </r>
+  </si>
+  <si>
     <r>
       <t>Manufacturer</t>
     </r>
@@ -172,28 +340,106 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">        Size         Type        </t>
-    </r>
-  </si>
-  <si>
-    <t>Ecore E-grip III Adhesive 4gal</t>
-  </si>
-  <si>
-    <t>Teknoflor Prevail 4000 Two Part Epoxy Adhesive (EX4000) 1gal</t>
-  </si>
-  <si>
-    <r>
-      <t>Base</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> – Other Relevant Information is gauge (thickness).  Additionally, we need to know the type (profile) of the base, the length, and if it is coils or pieces.  It is important to include the style# as it determines which type (profile) it is.</t>
+      <t xml:space="preserve">        Size         – Color (Color#)</t>
+    </r>
+  </si>
+  <si>
+    <t>Johnsonite Wheeled Traffic Transition (CTA-XX-JL) 12ft - Black (40)</t>
+  </si>
+  <si>
+    <t>Futura 3MM No-Lip Stair Nosing (LVT 340) 12ft - Etched Nickel (402019)</t>
+  </si>
+  <si>
+    <t>Mannington Fusion Transition Strip 2.5MM (720) 12ft - BlackBrown (523)</t>
+  </si>
+  <si>
+    <r>
+      <t>Vinyl Sheet Goods</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> – Other Relevant Information is thickness (if provided), usually single size (width).</t>
+    </r>
+  </si>
+  <si>
+    <t>Tarkett Standard Plus 6ft 6in 2.0MM - Light Grey (0497)</t>
+  </si>
+  <si>
+    <t>Forbo Flotex Metro 6ft 6in 4.3MM - Citrus (S246019)</t>
+  </si>
+  <si>
+    <t>Mannington BioSpec MD 6ft 6in 0.080in – Balsa (15359)</t>
+  </si>
+  <si>
+    <r>
+      <t>Vinyl Tile/Planks (LVT/LVP)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> – Other Relevant Information is thickness (if provided), two sizes (L x W).</t>
+    </r>
+  </si>
+  <si>
+    <t>Novalis Innovative Flooring AVA VRSE 9.84in x 39.37in 5.0MM - Minuet (VRS003L)</t>
+  </si>
+  <si>
+    <t>Cobalt Surfaces Petrous 7in x 48in 5.0MM - Willow (P20-416)</t>
+  </si>
+  <si>
+    <t>Shaw Patcraft Pursue (I633V) 7.09in x 47.24in 2.5MM - Restful-V2 (00720)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Manufacturer        Style       </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Style#)   </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">     Size </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">        Other Relevant Information          – Color (Color#)</t>
     </r>
   </si>
   <si>
@@ -251,112 +497,28 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">        Size         gauge    length  type       – Color (Color#)</t>
-    </r>
-  </si>
-  <si>
-    <t>Johnsonite Perceptions Recess (RWDC-XX) Cove Coil 4.25in x 120ft x 1/8in - Fawn (80)</t>
-  </si>
-  <si>
-    <t>Johnsonite Duracove Thermoplastic Rubber (DC-XX) Cove Pieces 6in x 4ft x 1/8in - Black (40)</t>
-  </si>
-  <si>
-    <t>Roppe Vinyl Wall Base Cove Pieces 4in x 4ft x 0.080in - White (170)</t>
-  </si>
-  <si>
-    <t>Mannington Edge Effects Cetera (EECET) Pieces 4in x 8ft x 5/16in - Jackalope (190)</t>
-  </si>
-  <si>
-    <r>
-      <t>Carpet (Broadloom)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> – Other Relevant Information is Backing, usually only a single size (width) provided.</t>
-    </r>
-  </si>
-  <si>
-    <t>Shaw Modify (5A204) 12ft Classicbac – Horizon (03496)</t>
-  </si>
-  <si>
-    <t>Mannington Gaskell 12ft 6in UltraBac RE – Debussy (42114)</t>
-  </si>
-  <si>
-    <t>Mohawk Eden Terrace (BC588) 12ft Weldlok – Twilight (575)</t>
-  </si>
-  <si>
-    <r>
-      <t>Carpet Tile</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> - Other Relevant Information is Backing, two sizes should be provided (L x W)</t>
-    </r>
-  </si>
-  <si>
-    <t>Shaw Habitat Tile (5T390) 9in x 36in Ecoworx - Still (88481)</t>
-  </si>
-  <si>
-    <t>Mohawk Stone Community (GT472) 12in x 36in EcoFlex ONE - Stone (949)</t>
-  </si>
-  <si>
-    <t>Flor Made You Look 50cm x 50cm CQuestGB - Ocean</t>
-  </si>
-  <si>
-    <r>
-      <t>Ceramic</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> – Other Relevant Information is Finish, but we also include what type of tile it is (field tile, bullnose, cove base, etc.).  Field tile often doesn’t have a style number, but sometimes the trim pieces do.  If there is a single item code for the piece, we would put it at the end as the color#.</t>
-    </r>
-  </si>
-  <si>
-    <t>TileBar Stonework Peak Field Tile 12in x 24in Satin - Black Jade</t>
-  </si>
-  <si>
-    <t>American Olean Color Story Cove Base Corner Left (SCL3361) 3in x 6in Glossy - Ice White (0025)</t>
-  </si>
-  <si>
-    <t>Daltile Advantage Field Tile 12in x 12in Matte - Mural Taupe (AQ02)</t>
-  </si>
-  <si>
-    <t>Daltile Synchronic Bullnose (P43F9) 3in x 24in Matte - White (SY30)</t>
-  </si>
-  <si>
-    <t>Floor &amp; Decor Hexagon Marble Mosaic 12in x 12in sheet Polished - Bianco Carrara (931100750)</t>
-  </si>
-  <si>
-    <r>
-      <t>Rubber Rolls</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> - Other Relevant Information is thickness (if provided), usually single size (width).</t>
+      <t xml:space="preserve">        Size         </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFEE0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Type</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">        </t>
     </r>
   </si>
   <si>
@@ -414,28 +576,28 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">        Size         Thickness          – Color (Color#)</t>
-    </r>
-  </si>
-  <si>
-    <t>Mondo Super X Performance 8MM 3ft 4in - Grey (P31)</t>
-  </si>
-  <si>
-    <t>Nora Noraplan Convia 48in 2.0MM - Pearl Grey (7351)</t>
-  </si>
-  <si>
-    <r>
-      <t>Rubber Tile</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> - Other Relevant Information is thickness (if provided), two sizes (L x W).</t>
+      <t xml:space="preserve">        Size         </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFEE0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Thickness</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">          – Color (Color#)</t>
     </r>
   </si>
   <si>
@@ -493,28 +655,28 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">        Size    thickness          – Color (Color#)</t>
-    </r>
-  </si>
-  <si>
-    <t>North West Rubber Ultimate Zip Tile 28.5in x 28.5in 9MM - Grey (5520400)</t>
-  </si>
-  <si>
-    <t>Mondo Sport Impact 6MM 36in x 36in Purple (026)</t>
-  </si>
-  <si>
-    <r>
-      <t>Transitions</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> – Other Relevant Information is generally not used.</t>
+      <t xml:space="preserve">        Size    </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFEE0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>thickness</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">          – Color (Color#)</t>
     </r>
   </si>
   <si>
@@ -572,72 +734,42 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">        Size         – Color (Color#)</t>
-    </r>
-  </si>
-  <si>
-    <t>Johnsonite Wheeled Traffic Transition (CTA-XX-JL) 12ft - Black (40)</t>
-  </si>
-  <si>
-    <t>Futura 3MM No-Lip Stair Nosing (LVT 340) 12ft - Etched Nickel (402019)</t>
-  </si>
-  <si>
-    <t>Mannington Fusion Transition Strip 2.5MM (720) 12ft - BlackBrown (523)</t>
-  </si>
-  <si>
-    <r>
-      <t>Vinyl Sheet Goods</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> – Other Relevant Information is thickness (if provided), usually single size (width).</t>
-    </r>
-  </si>
-  <si>
-    <t>Tarkett Standard Plus 6ft 6in 2.0MM - Light Grey (0497)</t>
-  </si>
-  <si>
-    <t>Forbo Flotex Metro 6ft 6in 4.3MM - Citrus (S246019)</t>
-  </si>
-  <si>
-    <t>Mannington BioSpec MD 6ft 6in 0.080in – Balsa (15359)</t>
-  </si>
-  <si>
-    <r>
-      <t>Vinyl Tile/Planks (LVT/LVP)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> – Other Relevant Information is thickness (if provided), two sizes (L x W).</t>
-    </r>
-  </si>
-  <si>
-    <t>Novalis Innovative Flooring AVA VRSE 9.84in x 39.37in 5.0MM - Minuet (VRS003L)</t>
-  </si>
-  <si>
-    <t>Cobalt Surfaces Petrous 7in x 48in 5.0MM - Willow (P20-416)</t>
-  </si>
-  <si>
-    <t>Shaw Patcraft Pursue (I633V) 7.09in x 47.24in 2.5MM - Restful-V2 (00720)</t>
+      <t xml:space="preserve">        Size         </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFEE0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>gauge    length  type</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">       – Color (Color#)</t>
+    </r>
+  </si>
+  <si>
+    <t>style = product_name</t>
+  </si>
+  <si>
+    <t>size =dimension (can be in weights and volume) -&gt; 1ADH is unique</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -672,6 +804,26 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFEE0000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -1051,21 +1203,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B41A4EAB-6CD0-48A1-A845-7AB4905103CD}">
   <dimension ref="A1:AG53"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:33">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:33">
+      <c r="E1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:33" s="5" customFormat="1">
+      <c r="E2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:33" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>2</v>
+        <v>44</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -1077,17 +1235,17 @@
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
     </row>
-    <row r="4" spans="1:33">
+    <row r="4" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:33">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
@@ -1099,27 +1257,27 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
     </row>
-    <row r="6" spans="1:33">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:33">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:33">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:33">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X9" s="4" t="s">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="Y9" s="3"/>
       <c r="Z9" s="3"/>
@@ -1131,34 +1289,34 @@
       <c r="AF9" s="3"/>
       <c r="AG9" s="3"/>
     </row>
-    <row r="10" spans="1:33">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:33">
-      <c r="A11" s="1" t="s">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:33">
-      <c r="A12" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:33">
-      <c r="A13" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:33">
+    <row r="14" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:33">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L15" s="4" t="s">
         <v>2</v>
@@ -1173,29 +1331,29 @@
       <c r="T15" s="3"/>
       <c r="U15" s="3"/>
     </row>
-    <row r="16" spans="1:33">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:21">
-      <c r="A17" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="18" spans="1:21">
-      <c r="A18" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="19" spans="1:21">
+    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:21">
+    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="L20" s="4" t="s">
         <v>2</v>
@@ -1210,65 +1368,65 @@
       <c r="T20" s="3"/>
       <c r="U20" s="3"/>
     </row>
-    <row r="21" spans="1:21">
+    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="1:21">
-      <c r="A22" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="23" spans="1:21">
-      <c r="A23" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="24" spans="1:21">
+    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:21">
+    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="26" spans="1:21">
-      <c r="A26" s="1" t="s">
+    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="27" spans="1:21">
-      <c r="A27" s="1" t="s">
+    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="28" spans="1:21">
-      <c r="A28" s="1" t="s">
+    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="29" spans="1:21">
-      <c r="A29" s="1" t="s">
+    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A31" s="1"/>
+    </row>
+    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="30" spans="1:21">
-      <c r="A30" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="31" spans="1:21">
-      <c r="A31" s="1"/>
-    </row>
-    <row r="32" spans="1:21">
-      <c r="A32" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="L32" s="4" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="M32" s="3"/>
       <c r="N32" s="3"/>
@@ -1280,27 +1438,27 @@
       <c r="T32" s="3"/>
       <c r="U32" s="3"/>
     </row>
-    <row r="33" spans="1:21">
+    <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="34" spans="1:21">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="35" spans="1:21">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:21">
+    <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="L36" s="4" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="M36" s="3"/>
       <c r="N36" s="3"/>
@@ -1312,27 +1470,27 @@
       <c r="T36" s="3"/>
       <c r="U36" s="3"/>
     </row>
-    <row r="37" spans="1:21">
+    <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="38" spans="1:21">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="39" spans="1:21">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:21">
+    <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="L40" s="4" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
@@ -1344,32 +1502,32 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
     </row>
-    <row r="41" spans="1:21">
+    <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="42" spans="1:21">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="43" spans="1:21">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="44" spans="1:21">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:21">
+    <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="L45" s="4" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="M45" s="3"/>
       <c r="N45" s="3"/>
@@ -1380,32 +1538,32 @@
       <c r="S45" s="3"/>
       <c r="T45" s="3"/>
     </row>
-    <row r="46" spans="1:21">
+    <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="47" spans="1:21">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="48" spans="1:21">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="49" spans="1:20">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="49" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:20">
+    <row r="50" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="L50" s="4" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="M50" s="3"/>
       <c r="N50" s="3"/>
@@ -1416,19 +1574,19 @@
       <c r="S50" s="3"/>
       <c r="T50" s="3"/>
     </row>
-    <row r="51" spans="1:20">
+    <row r="51" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="52" spans="1:20">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="52" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="53" spans="1:20">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="53" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -1439,19 +1597,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1EC8E7F-D23C-4CC2-9C51-E795516AFDBF}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1656,19 +1811,46 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6DDA1754-AB42-418C-8A14-BFC6EC28B98D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{341261EB-4C18-4F73-B2C1-1D1EB20C3AE6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A942EA02-F89E-49DF-941F-D6CA88E1DF44}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A942EA02-F89E-49DF-941F-D6CA88E1DF44}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="28cf399f-4fb4-4244-a8f8-d731515ce28b"/>
+    <ds:schemaRef ds:uri="bc2b4c79-9e4f-46e6-b513-a54784642b7a"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{341261EB-4C18-4F73-B2C1-1D1EB20C3AE6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6DDA1754-AB42-418C-8A14-BFC6EC28B98D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>